--- a/KPWL_Problems/MIP_Solver/out_non_sym/results_2025-03-31.xlsx
+++ b/KPWL_Problems/MIP_Solver/out_non_sym/results_2025-03-31.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,6 +1256,356 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cw1.txt</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>600.6577360630035</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gcut8.txt</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>602.853621006012</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>okp1.txt</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>118.2121331691742</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>21960</v>
+      </c>
+      <c r="G27" t="n">
+        <v>480</v>
+      </c>
+      <c r="H27" t="n">
+        <v>557</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23638</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>okp3.txt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>600.5044310092926</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>okp2.txt</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>600.3721323013306</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>r_20_s.txt</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>600.6542358398438</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>9525</v>
+      </c>
+      <c r="G30" t="n">
+        <v>840</v>
+      </c>
+      <c r="H30" t="n">
+        <v>992</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>r_20_l.txt</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>600.235054731369</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cu2.txt</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>601.1202750205994</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cu3.txt</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>600.8687171936035</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cu1.txt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mip_rotate_symmetry</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>600.3034491539001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
